--- a/artfynd/A 33806-2023 artfynd.xlsx
+++ b/artfynd/A 33806-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33806-2023 artfynd.xlsx
+++ b/artfynd/A 33806-2023 artfynd.xlsx
@@ -675,53 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91131824</v>
+        <v>113034475</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2014</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mårtviksberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529029.7814175301</v>
+        <v>529213</v>
       </c>
       <c r="R2" t="n">
-        <v>7028919.958532283</v>
+        <v>7029361</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,47 +757,48 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kalktallskog</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Cecilia Odelberg</t>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113033429</v>
+        <v>113033426</v>
       </c>
       <c r="B3" t="n">
-        <v>90063</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>3739</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529116</v>
+        <v>529175</v>
       </c>
       <c r="R3" t="n">
-        <v>7029045</v>
+        <v>7028949</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,15 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113034447</v>
+        <v>113034452</v>
       </c>
       <c r="B4" t="n">
-        <v>79184</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,27 +907,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>4412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mårtviksberget, Jmt</t>
@@ -988,35 +969,14 @@
           <t>2023-09-27</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På grov gammal björk</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1037,37 +997,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113034452</v>
+        <v>113034477</v>
       </c>
       <c r="B5" t="n">
-        <v>86862</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4412</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1077,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529194</v>
+        <v>529349</v>
       </c>
       <c r="R5" t="n">
-        <v>7029392</v>
+        <v>7028812</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,50 +1098,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113033473</v>
+        <v>113034447</v>
       </c>
       <c r="B6" t="n">
-        <v>97314</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mårtviksberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529117</v>
+        <v>529194</v>
       </c>
       <c r="R6" t="n">
-        <v>7029002</v>
+        <v>7029392</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,12 +1166,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På grov gammal björk</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,8 +1185,24 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1249,53 +1223,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113034475</v>
+        <v>113033473</v>
       </c>
       <c r="B7" t="n">
-        <v>90827</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2014</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Pers.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mårtviksberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529213</v>
+        <v>529118</v>
       </c>
       <c r="R7" t="n">
-        <v>7029361</v>
+        <v>7029003</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,12 +1288,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,24 +1302,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1374,37 +1324,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113033426</v>
+        <v>91131824</v>
       </c>
       <c r="B8" t="n">
-        <v>85927</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3739</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1414,13 +1359,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529175</v>
+        <v>529030</v>
       </c>
       <c r="R8" t="n">
-        <v>7028949</v>
+        <v>7028920</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,12 +1389,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2019-07-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2019-07-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,21 +1405,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalktallskog</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Cecilia Odelberg</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+          <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 33806-2023 artfynd.xlsx
+++ b/artfynd/A 33806-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -792,6 +797,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034475</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113033426</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034452</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034477</t>
         </is>
       </c>
     </row>
@@ -1220,6 +1245,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034447</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113033473</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1432,8 +1467,22 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131824</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>